--- a/ch_01_getting_started/ch_01.xlsx
+++ b/ch_01_getting_started/ch_01.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29809"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wiley.sharepoint.com/teams/9781394284931MountExcelPowerTools/Shared Documents/General/Stage1_ContentDevelopment/01_originalmaterialfromAU/code_files/ch09-python-in-excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\AI-Powered-Analytics-in-Excel\ch_01_getting_started\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{BBCB87A6-238B-470F-B240-58026FEDDFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A8105C4-FD5A-4095-827B-A1E5E7FD13AF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8035CB10-D9FB-4B1E-9767-591C7A36109B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hello-world" sheetId="2" r:id="rId1"/>
-    <sheet name="nyc-pop" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,35 +53,6 @@
     </initialization>
   </environmentDefinition>
 </python>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>borough</t>
-  </si>
-  <si>
-    <t>population</t>
-  </si>
-  <si>
-    <t>land_area</t>
-  </si>
-  <si>
-    <t>Brooklyn</t>
-  </si>
-  <si>
-    <t>Queens</t>
-  </si>
-  <si>
-    <t>Manhattan</t>
-  </si>
-  <si>
-    <t>The Bronx</t>
-  </si>
-  <si>
-    <t>Staten Island</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -116,18 +86,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -138,18 +103,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A10AA66D-0CEA-45C5-980F-5E74931B4CB6}" name="Table1" displayName="Table1" ref="A1:C6" totalsRowShown="0">
-  <autoFilter ref="A1:C6" xr:uid="{A10AA66D-0CEA-45C5-980F-5E74931B4CB6}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1C4F4E5A-700D-4ED4-B798-004411B112D2}" name="borough"/>
-    <tableColumn id="2" xr3:uid="{0D43E266-7ECD-471E-9C37-806A4723D376}" name="population" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{E15CEA82-3240-498B-A533-B74986C73C21}" name="land_area"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -500,106 +453,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{249EE3E8-639D-4031-B70D-8C339EC092A9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.53125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" customWidth="1"/>
-    <col min="5" max="5" width="11.46484375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1">
-        <v>2736074</v>
-      </c>
-      <c r="C2">
-        <v>69.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2405464</v>
-      </c>
-      <c r="C3">
-        <v>108.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1694251</v>
-      </c>
-      <c r="C4">
-        <v>22.83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1472654</v>
-      </c>
-      <c r="C5">
-        <v>42.1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
-        <v>495747</v>
-      </c>
-      <c r="C6">
-        <v>58.37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d1092ee-e153-45fa-8899-22e30fa0d204">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="8da6c5d4-83a2-44cb-9fdf-dd797777f83e" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -798,21 +664,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3d1092ee-e153-45fa-8899-22e30fa0d204">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="8da6c5d4-83a2-44cb-9fdf-dd797777f83e" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56E80942-063A-47D3-9D66-206AC1FA005E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC6DA2B5-11A2-4A25-AEE7-F2A37797545F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3d1092ee-e153-45fa-8899-22e30fa0d204"/>
-    <ds:schemaRef ds:uri="8da6c5d4-83a2-44cb-9fdf-dd797777f83e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -837,9 +702,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC6DA2B5-11A2-4A25-AEE7-F2A37797545F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56E80942-063A-47D3-9D66-206AC1FA005E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3d1092ee-e153-45fa-8899-22e30fa0d204"/>
+    <ds:schemaRef ds:uri="8da6c5d4-83a2-44cb-9fdf-dd797777f83e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>